--- a/database/CMS_Produk_MitraAbadi_Update.xlsx
+++ b/database/CMS_Produk_MitraAbadi_Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2025\PT MASFOOD WEB\mitra-abadi\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9722DA8E-46DC-4959-8599-714A563A6DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04215041-D458-42AA-BA16-F57B9057EAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2476,7 +2476,8 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30.375" customWidth="1"/>
-    <col min="6" max="6" width="54.75" customWidth="1"/>
+    <col min="6" max="6" width="67" customWidth="1"/>
+    <col min="7" max="7" width="90.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">

--- a/database/CMS_Produk_MitraAbadi_Update.xlsx
+++ b/database/CMS_Produk_MitraAbadi_Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2025\PT MASFOOD WEB\mitra-abadi\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B5B9D3-D358-4EA1-87E9-E3E939251F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE3A2FB-6E6C-460C-BB20-D94F9A8017ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2445" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="700">
   <si>
     <t>ID</t>
   </si>
@@ -2114,6 +2114,12 @@
   </si>
   <si>
     <t>Potato Crisps Wavy Mexican Hot Sauce Cans 110g</t>
+  </si>
+  <si>
+    <t>assets/images/products/jacker/hot-spicy-flavor-potato-chips60gr.png</t>
+  </si>
+  <si>
+    <t>assets/images/products/jacker/barbecue-flavor-potato-chips60gr.png</t>
   </si>
 </sst>
 </file>
@@ -2129,7 +2135,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2151,6 +2157,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2182,13 +2194,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3626,7 +3639,7 @@
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="6" t="s">
         <v>678</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -3638,7 +3651,9 @@
       <c r="E32" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F32" s="2"/>
+      <c r="F32" s="3" t="s">
+        <v>698</v>
+      </c>
       <c r="G32" s="1" t="s">
         <v>91</v>
       </c>
@@ -3659,7 +3674,7 @@
       <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="6" t="s">
         <v>677</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -3671,7 +3686,9 @@
       <c r="E33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F33" s="2"/>
+      <c r="F33" s="2" t="s">
+        <v>699</v>
+      </c>
       <c r="G33" s="1" t="s">
         <v>93</v>
       </c>
@@ -3692,7 +3709,7 @@
       <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="6" t="s">
         <v>94</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -3727,7 +3744,7 @@
       <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="6" t="s">
         <v>679</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -11112,7 +11129,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K1 A7:K17 A6 C6:E6 A5 C5:E5 G5:K5 G6:K6 A100:K100 A99:E99 G99:H99 A102:K105 A101:E101 G101:K101 A98:E98 G98:H98 J98:K98 J99:K99 A107:K108 A106 C106:K106 A110:K130 A109 C109:K109 A132:E132 A131 C131:K131 A135:K165 A133:E133 G133:K133 G132:K132 A134:E134 G134:K134 A34:E34 A31 J31:K31 G31:H31 C31:E31 A196:K245 A195:E195 G195:K195 A181:K194 A180:E180 G180:K180 A167:K179 A166:E166 G166:K166 A32 C32:E32 G32:K32 A33 C33:E33 A36:K97 A35 C35:E35 A30 C30:E30 G30:K30 G33:K33 G34:K34 G35:K35 A29 A24 C24:K24 A23 A18 C18:K18 A19 C19:K19 A20 C20:K20 A21 C21:K21 A22 C22:K22 C23:K23 A25 C25:K25 A26 C26:K26 A27 C27:K27 A28 C28:K28 C29:K29 A3:K4 A2 C2:K2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:K1 A7:K17 A6 C6:E6 A5 C5:E5 G5:K5 G6:K6 A100:K100 A99:E99 G99:H99 A102:K105 A101:E101 G101:K101 A98:E98 G98:H98 J98:K98 J99:K99 A107:K108 A106 C106:K106 A110:K130 A109 C109:K109 A132:E132 A131 C131:K131 A135:K165 A133:E133 G133:K133 G132:K132 A134:E134 G134:K134 A34:E34 A31 J31:K31 G31:H31 C31:E31 A196:K245 A195:E195 G195:K195 A181:K194 A180:E180 G180:K180 A167:K179 A166:E166 G166:K166 A32 C32:E32 G32:K32 A33 C33:E33 A36:K97 A35 C35:E35 A30 C30:E30 G30:K30 G33:K33 G34:K34 G35:K35 A29 A24 C24:K24 A23 A18 C18:K18 A19 C19:K19 A20 C20:K20 A21 C21:K21 A22 C22:K22 C23:K23 A25 C25:K25 A26 C26:E26 A27 C27:K27 A28 C28:K28 C29:K29 A3:K4 A2 C2:K2 G26:K26" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/database/CMS_Produk_MitraAbadi_Update.xlsx
+++ b/database/CMS_Produk_MitraAbadi_Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2025\PT MASFOOD WEB\mitra-abadi\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C89A872-518F-4A2E-A103-67038B51F4B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642AF018-F195-4FA6-9E70-F1C55B667ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2464,9 +2464,6 @@
     <t>assets/images/products/kiss-delicias/ice-lolly-shaped-lollipop-strawberry-flavor60gr.png</t>
   </si>
   <si>
-    <t>KISS DELICIAS Ice Lolly Shaped Lollipop Strawberry Flavor adalah camilan bahan-bahan pilihan dengan cita rasa autentik yang khas. Dibuat dari bahan-bahan bermutu dengan tekstur renyah, setiap gigitannya menghadirkan pengalaman rasa yang kaya dan memuaskan. Pilihan praktis dan nikmat bagi Anda yang menginginkan camilan lezat berkualitas untuk menemani setiap momen.</t>
-  </si>
-  <si>
     <t>Q-Jin Dried Tofu Barbeque Flavor</t>
   </si>
   <si>
@@ -2626,10 +2623,13 @@
     <t>HUANG XIAO GU! Instant Noodle Original adalah camilan mie kering bahan-bahan pilihan dengan original klasik snack yang siap di makan langsung</t>
   </si>
   <si>
-    <t>MASTER JH Gummy Candy Assorted adalah permen lunak dengan aneka rasa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MASTER JH Orange Soft Candy adalah  permen lunak rasa jeruk </t>
+    <t xml:space="preserve">MASTER JH Gummy Candy Assorted adalah permen lunak lembut berisi fill dengan aneka rasa mempunyai kemasan yang menarik </t>
+  </si>
+  <si>
+    <t>MASTER JH Orange Soft Candy adalah  permen lunak rasa jeruk kenyal manis beraroma jeruk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KISS DELICIAS Ice Lolly Shaped Lollipop Strawberry Flavor adalah </t>
   </si>
 </sst>
 </file>
@@ -2974,7 +2974,7 @@
   <cols>
     <col min="2" max="2" width="42" customWidth="1"/>
     <col min="5" max="5" width="22.140625" customWidth="1"/>
-    <col min="6" max="6" width="90.28515625" customWidth="1"/>
+    <col min="6" max="6" width="94.7109375" customWidth="1"/>
     <col min="7" max="7" width="185.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3593,7 +3593,7 @@
         <v>75</v>
       </c>
       <c r="G18" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
@@ -3628,7 +3628,7 @@
         <v>79</v>
       </c>
       <c r="G19" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
@@ -3663,7 +3663,7 @@
         <v>81</v>
       </c>
       <c r="G20" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
@@ -3698,7 +3698,7 @@
         <v>83</v>
       </c>
       <c r="G21" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
@@ -3733,7 +3733,7 @@
         <v>85</v>
       </c>
       <c r="G22" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
@@ -3768,7 +3768,7 @@
         <v>87</v>
       </c>
       <c r="G23" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
@@ -3803,7 +3803,7 @@
         <v>89</v>
       </c>
       <c r="G24" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
@@ -3838,7 +3838,7 @@
         <v>90</v>
       </c>
       <c r="G25" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
@@ -3873,7 +3873,7 @@
         <v>92</v>
       </c>
       <c r="G26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
@@ -3908,7 +3908,7 @@
         <v>93</v>
       </c>
       <c r="G27" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H27" t="s">
         <v>17</v>
@@ -3943,7 +3943,7 @@
         <v>94</v>
       </c>
       <c r="G28" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
@@ -3978,7 +3978,7 @@
         <v>95</v>
       </c>
       <c r="G29" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H29" t="s">
         <v>17</v>
@@ -4013,7 +4013,7 @@
         <v>97</v>
       </c>
       <c r="G30" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
@@ -4048,7 +4048,7 @@
         <v>100</v>
       </c>
       <c r="G31" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H31" t="s">
         <v>17</v>
@@ -4083,7 +4083,7 @@
         <v>104</v>
       </c>
       <c r="G32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H32" t="s">
         <v>17</v>
@@ -4118,7 +4118,7 @@
         <v>107</v>
       </c>
       <c r="G33" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H33" t="s">
         <v>17</v>
@@ -4153,7 +4153,7 @@
         <v>109</v>
       </c>
       <c r="G34" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
@@ -5378,7 +5378,7 @@
         <v>236</v>
       </c>
       <c r="G69" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H69" t="s">
         <v>17</v>
@@ -5413,7 +5413,7 @@
         <v>240</v>
       </c>
       <c r="G70" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H70" t="s">
         <v>17</v>
@@ -5448,7 +5448,7 @@
         <v>242</v>
       </c>
       <c r="G71" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H71" t="s">
         <v>17</v>
@@ -5483,7 +5483,7 @@
         <v>244</v>
       </c>
       <c r="G72" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H72" t="s">
         <v>17</v>
@@ -5518,7 +5518,7 @@
         <v>246</v>
       </c>
       <c r="G73" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H73" t="s">
         <v>17</v>
@@ -5553,7 +5553,7 @@
         <v>248</v>
       </c>
       <c r="G74" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H74" t="s">
         <v>17</v>
@@ -5588,7 +5588,7 @@
         <v>250</v>
       </c>
       <c r="G75" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H75" t="s">
         <v>17</v>
@@ -5623,7 +5623,7 @@
         <v>252</v>
       </c>
       <c r="G76" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H76" t="s">
         <v>17</v>
@@ -5658,7 +5658,7 @@
         <v>254</v>
       </c>
       <c r="G77" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H77" t="s">
         <v>17</v>
@@ -5693,7 +5693,7 @@
         <v>255</v>
       </c>
       <c r="G78" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H78" t="s">
         <v>17</v>
@@ -5728,7 +5728,7 @@
         <v>257</v>
       </c>
       <c r="G79" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H79" t="s">
         <v>17</v>
@@ -5763,7 +5763,7 @@
         <v>258</v>
       </c>
       <c r="G80" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H80" t="s">
         <v>17</v>
@@ -5798,7 +5798,7 @@
         <v>259</v>
       </c>
       <c r="G81" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H81" t="s">
         <v>17</v>
@@ -5833,7 +5833,7 @@
         <v>260</v>
       </c>
       <c r="G82" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H82" t="s">
         <v>17</v>
@@ -5868,7 +5868,7 @@
         <v>261</v>
       </c>
       <c r="G83" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H83" t="s">
         <v>17</v>
@@ -5903,7 +5903,7 @@
         <v>262</v>
       </c>
       <c r="G84" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H84" t="s">
         <v>17</v>
@@ -5938,7 +5938,7 @@
         <v>263</v>
       </c>
       <c r="G85" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H85" t="s">
         <v>17</v>
@@ -5973,7 +5973,7 @@
         <v>264</v>
       </c>
       <c r="G86" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H86" t="s">
         <v>17</v>
@@ -6218,7 +6218,7 @@
         <v>288</v>
       </c>
       <c r="G93" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H93" t="s">
         <v>17</v>
@@ -6253,7 +6253,7 @@
         <v>292</v>
       </c>
       <c r="G94" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H94" t="s">
         <v>17</v>
@@ -6288,7 +6288,7 @@
         <v>294</v>
       </c>
       <c r="G95" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H95" t="s">
         <v>17</v>
@@ -6323,7 +6323,7 @@
         <v>296</v>
       </c>
       <c r="G96" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H96" t="s">
         <v>17</v>
@@ -6358,7 +6358,7 @@
         <v>299</v>
       </c>
       <c r="G97" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H97" t="s">
         <v>17</v>
@@ -6393,7 +6393,7 @@
         <v>301</v>
       </c>
       <c r="G98" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H98" t="s">
         <v>17</v>
@@ -6428,7 +6428,7 @@
         <v>304</v>
       </c>
       <c r="G99" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H99" t="s">
         <v>17</v>
@@ -6463,7 +6463,7 @@
         <v>306</v>
       </c>
       <c r="G100" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H100" t="s">
         <v>17</v>
@@ -6498,7 +6498,7 @@
         <v>309</v>
       </c>
       <c r="G101" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H101" t="s">
         <v>17</v>
@@ -6533,7 +6533,7 @@
         <v>312</v>
       </c>
       <c r="G102" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H102" t="s">
         <v>17</v>
@@ -6568,7 +6568,7 @@
         <v>314</v>
       </c>
       <c r="G103" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H103" t="s">
         <v>17</v>
@@ -6603,7 +6603,7 @@
         <v>316</v>
       </c>
       <c r="G104" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H104" t="s">
         <v>17</v>
@@ -6638,7 +6638,7 @@
         <v>320</v>
       </c>
       <c r="G105" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H105" t="s">
         <v>17</v>
@@ -6673,7 +6673,7 @@
         <v>322</v>
       </c>
       <c r="G106" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H106" t="s">
         <v>17</v>
@@ -6708,7 +6708,7 @@
         <v>323</v>
       </c>
       <c r="G107" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H107" t="s">
         <v>17</v>
@@ -6743,7 +6743,7 @@
         <v>325</v>
       </c>
       <c r="G108" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H108" t="s">
         <v>17</v>
@@ -6778,7 +6778,7 @@
         <v>326</v>
       </c>
       <c r="G109" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H109" t="s">
         <v>17</v>
@@ -7583,7 +7583,7 @@
         <v>423</v>
       </c>
       <c r="G132" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H132" t="s">
         <v>369</v>
@@ -7618,7 +7618,7 @@
         <v>426</v>
       </c>
       <c r="G133" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H133" t="s">
         <v>369</v>
@@ -7653,7 +7653,7 @@
         <v>431</v>
       </c>
       <c r="G134" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H134" t="s">
         <v>369</v>
@@ -7688,7 +7688,7 @@
         <v>435</v>
       </c>
       <c r="G135" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H135" t="s">
         <v>369</v>
@@ -11359,7 +11359,7 @@
         <v>813</v>
       </c>
       <c r="G241" t="s">
-        <v>814</v>
+        <v>869</v>
       </c>
       <c r="H241" t="s">
         <v>369</v>
@@ -11379,34 +11379,34 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C242" t="s">
         <v>12</v>
       </c>
       <c r="D242" t="s">
+        <v>815</v>
+      </c>
+      <c r="E242" t="s">
         <v>816</v>
       </c>
-      <c r="E242" t="s">
+      <c r="F242" t="s">
         <v>817</v>
       </c>
-      <c r="F242" t="s">
-        <v>818</v>
-      </c>
       <c r="G242" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H242" t="s">
         <v>369</v>
       </c>
       <c r="I242" t="s">
+        <v>818</v>
+      </c>
+      <c r="J242" t="s">
+        <v>19</v>
+      </c>
+      <c r="K242" t="s">
         <v>819</v>
-      </c>
-      <c r="J242" t="s">
-        <v>19</v>
-      </c>
-      <c r="K242" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
@@ -11414,34 +11414,34 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C243" t="s">
         <v>12</v>
       </c>
       <c r="D243" t="s">
+        <v>815</v>
+      </c>
+      <c r="E243" t="s">
         <v>816</v>
       </c>
-      <c r="E243" t="s">
-        <v>817</v>
-      </c>
       <c r="F243" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="G243" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H243" t="s">
         <v>369</v>
       </c>
       <c r="I243" t="s">
+        <v>818</v>
+      </c>
+      <c r="J243" t="s">
+        <v>19</v>
+      </c>
+      <c r="K243" t="s">
         <v>819</v>
-      </c>
-      <c r="J243" t="s">
-        <v>19</v>
-      </c>
-      <c r="K243" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -11449,34 +11449,34 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C244" t="s">
         <v>12</v>
       </c>
       <c r="D244" t="s">
+        <v>815</v>
+      </c>
+      <c r="E244" t="s">
         <v>816</v>
       </c>
-      <c r="E244" t="s">
-        <v>817</v>
-      </c>
       <c r="F244" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="G244" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H244" t="s">
         <v>369</v>
       </c>
       <c r="I244" t="s">
+        <v>818</v>
+      </c>
+      <c r="J244" t="s">
+        <v>19</v>
+      </c>
+      <c r="K244" t="s">
         <v>819</v>
-      </c>
-      <c r="J244" t="s">
-        <v>19</v>
-      </c>
-      <c r="K244" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -11484,34 +11484,34 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C245" t="s">
         <v>12</v>
       </c>
       <c r="D245" t="s">
+        <v>815</v>
+      </c>
+      <c r="E245" t="s">
         <v>816</v>
       </c>
-      <c r="E245" t="s">
-        <v>817</v>
-      </c>
       <c r="F245" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G245" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H245" t="s">
         <v>369</v>
       </c>
       <c r="I245" t="s">
+        <v>818</v>
+      </c>
+      <c r="J245" t="s">
+        <v>19</v>
+      </c>
+      <c r="K245" t="s">
         <v>819</v>
-      </c>
-      <c r="J245" t="s">
-        <v>19</v>
-      </c>
-      <c r="K245" t="s">
-        <v>820</v>
       </c>
     </row>
   </sheetData>
